--- a/data/trans_bre/P1421-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1421-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>105,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,39</t>
+          <t>-0,73; 2,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,49</t>
+          <t>4,15; 8,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,79</t>
+          <t>0,92; 4,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,79</t>
+          <t>2,46; 7,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 243,76</t>
+          <t>-37,37; 251,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>228,28; 1617,21</t>
+          <t>243,53; 1895,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,05; 440,21</t>
+          <t>17,81; 459,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,98; 190,34</t>
+          <t>40,14; 222,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>208,47%</t>
+          <t>155,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,49</t>
+          <t>0,92; 4,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,29</t>
+          <t>2,25; 5,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,64</t>
+          <t>3,25; 6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,01</t>
+          <t>3,37; 7,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,84; 242,55</t>
+          <t>27,53; 249,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>129,9; 871,34</t>
+          <t>118,77; 812,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>206,59; 1155,32</t>
+          <t>224,13; 1147,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,16; 495,8</t>
+          <t>64,75; 278,08</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>123,3%</t>
+          <t>197,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,04</t>
+          <t>2,66; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,29</t>
+          <t>2,26; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,22</t>
+          <t>1,71; 5,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 9,66</t>
+          <t>6,3; 11,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,39; 575,14</t>
+          <t>78,84; 525,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>102,93; 1102,5</t>
+          <t>97,24; 1137,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,91; 623,97</t>
+          <t>64,22; 671,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 246,3</t>
+          <t>105,83; 352,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>114,84%</t>
+          <t>135,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,89</t>
+          <t>2,74; 6,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,9</t>
+          <t>1,64; 4,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,28</t>
+          <t>2,71; 6,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,14</t>
+          <t>4,73; 9,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,61; 288,7</t>
+          <t>69,05; 309,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,85; 433,09</t>
+          <t>63,62; 430,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>112,48; 576,37</t>
+          <t>112,86; 609,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,93; 205,82</t>
+          <t>66,83; 226,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>139,14%</t>
+          <t>149,38%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,37</t>
+          <t>2,45; 4,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,05</t>
+          <t>3,31; 5,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,04</t>
+          <t>3,15; 4,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,69</t>
+          <t>5,55; 7,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,9; 221,76</t>
+          <t>86,83; 214,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>223,98; 566,26</t>
+          <t>219,39; 524,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>184,12; 429,99</t>
+          <t>183,57; 449,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 210,62</t>
+          <t>105,0; 201,19</t>
         </is>
       </c>
     </row>
